--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>164241</t>
+          <t>90807</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>104313</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>204138</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>201960</t>
+          <t>102136</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>199439</t>
+          <t>99922</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>195927</t>
+          <t>98624</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>250910</t>
+          <t>154905</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>341398</t>
+          <t>189112</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>431360</t>
+          <t>244867</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>497317</t>
+          <t>255069</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>519239</t>
+          <t>266789</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>541198</t>
+          <t>277028</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>558822</t>
+          <t>284413</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>558405</t>
+          <t>276612</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>542493</t>
+          <t>268500</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>534381</t>
+          <t>268500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
